--- a/config/union_qa/qa_question.xlsx
+++ b/config/union_qa/qa_question.xlsx
@@ -28787,7 +28787,7 @@
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>朋友</t>
+          <t>好友</t>
         </is>
       </c>
       <c r="U188" t="inlineStr">
@@ -33449,7 +33449,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>是王者的证明，受同伴尊敬</t>
+          <t>是王者的证明，受伙伴尊敬</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -34640,7 +34640,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>圆蝌蚪一般使用什么方法告知同伴有危险？</t>
+          <t>圆蝌蚪一般使用什么方法告知伙伴有危险？</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
